--- a/results/Int Task Remove ACC 0.6/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC 0.6/Rando_9_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8030198736277313</v>
+        <v>0.8266043630202267</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.805146669490628</v>
+        <v>0.8457190511489993</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8033816936707967</v>
+        <v>0.8433936955063716</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7957128737336299</v>
+        <v>0.8410683398637439</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7926285784884747</v>
+        <v>0.8410683398637439</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7785440714462212</v>
+        <v>0.8363514419852448</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.773200607151682</v>
+        <v>0.7997061315259981</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.790616506053867</v>
+        <v>0.8023447703766458</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.79665272335769</v>
+        <v>0.8120433125066187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7956466871403862</v>
+        <v>0.8468574605527904</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7999179286243778</v>
+        <v>0.8258630731758975</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7827491263369692</v>
+        <v>0.8194650358290092</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8092193511948886</v>
+        <v>0.8053143421935119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8079000317695648</v>
+        <v>0.8015549436972713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8075867485615447</v>
+        <v>0.7856569240001412</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8112976102227399</v>
+        <v>0.7753627025309753</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8133096826573476</v>
+        <v>0.7746037629284479</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8143157188746515</v>
+        <v>0.7632240813300858</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8146951886759151</v>
+        <v>0.7653508771929824</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.792562391895231</v>
+        <v>0.7653508771929824</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7955805005471425</v>
+        <v>0.7653508771929824</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7887191570475485</v>
+        <v>0.7479349782907974</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8102253874121925</v>
+        <v>0.7287541035687811</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7749479332133149</v>
+        <v>0.7201630837657524</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7749479332133149</v>
+        <v>0.7233929895160436</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7752612164213351</v>
+        <v>0.7344593879063857</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7655141374563168</v>
+        <v>0.7022000423594197</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7595441067457376</v>
+        <v>0.6994952169155282</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7668996434748844</v>
+        <v>0.7128869709484981</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7521223834233471</v>
+        <v>0.7119471213244378</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7531284196406509</v>
+        <v>0.7114529280948851</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.751579653358749</v>
+        <v>0.7109410851071341</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7076935295986445</v>
+        <v>0.6607539976702319</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7051210773412404</v>
+        <v>0.6550972501676727</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7051210773412404</v>
+        <v>0.6561032863849765</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7112720180733524</v>
+        <v>0.641705496134703</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6962476614070388</v>
+        <v>0.641705496134703</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6995790532669702</v>
+        <v>0.6359825620389</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.69801263722687</v>
+        <v>0.6509583818701684</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6980788238201137</v>
+        <v>0.6489463094355608</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6980788238201137</v>
+        <v>0.626747326061633</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6980788238201137</v>
+        <v>0.6307714709308483</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6629337428077235</v>
+        <v>0.6307714709308483</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6810115076423453</v>
+        <v>0.6230364644004377</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.682970630802358</v>
+        <v>0.6364282184334075</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.685031240072011</v>
+        <v>0.6203316389565463</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6340366761975361</v>
+        <v>0.6197050725405062</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5694164989939637</v>
+        <v>0.6175606269194112</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5633802816901409</v>
+        <v>0.5803372868791697</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5540126725263864</v>
+        <v>0.5813433230964735</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5567174979702778</v>
+        <v>0.5816566063044937</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5671573299445798</v>
+        <v>0.5617829785731936</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5651452575099721</v>
+        <v>0.5711020509019027</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5661512937272759</v>
+        <v>0.560282749126337</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5543921423276501</v>
+        <v>0.5829759257298175</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5862720180733524</v>
+        <v>0.5779457446432984</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5710005647922624</v>
+        <v>0.5107884146987186</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5704401849694659</v>
+        <v>0.5114811677080024</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5343376045748173</v>
+        <v>0.5088425288573546</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5354098273853648</v>
+        <v>0.5088425288573546</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5347832609693247</v>
+        <v>0.5128004871333263</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5200060009177875</v>
+        <v>0.5047521973948957</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5003794698012637</v>
+        <v>0.5024930283455117</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4988792403544072</v>
+        <v>0.5028724981467754</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4977584807088143</v>
+        <v>0.5028724981467754</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4889203642910092</v>
+        <v>0.4973304740725052</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4889203642910092</v>
+        <v>0.4963244378552014</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.499885276571711</v>
+        <v>0.4966377210632214</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4995058067704473</v>
+        <v>0.4970833774577288</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4995058067704473</v>
+        <v>0.5036314377493029</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4995058067704473</v>
+        <v>0.5006927530092837</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5006927530092837</v>
+        <v>0.4988130537611635</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5023915422358713</v>
+        <v>0.4988130537611635</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5023915422358713</v>
+        <v>0.4981203007518797</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5006927530092837</v>
+        <v>0.4974937343358396</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5016987892265876</v>
+        <v>0.4924812030075188</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5016987892265876</v>
+        <v>0.4934210526315789</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.4993734335839599</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.4968671679197995</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.4968671679197995</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.4971804511278196</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.4968671679197995</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.4959273182957393</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4993734335839599</v>
+        <v>0.4965538847117795</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4993734335839599</v>
+        <v>0.4974937343358396</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4993734335839599</v>
+        <v>0.4974937343358396</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4993734335839599</v>
+        <v>0.4978732041371033</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.4978732041371033</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5006927530092837</v>
+        <v>0.4974937343358396</v>
       </c>
     </row>
   </sheetData>
